--- a/BWI/bestwine_output/bestwine_South Korea.xlsx
+++ b/BWI/bestwine_output/bestwine_South Korea.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA153"/>
+  <dimension ref="A1:AA154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16633,6 +16633,99 @@
       <c r="Z153" s="2" t="inlineStr"/>
       <c r="AA153" s="2" t="inlineStr"/>
     </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Jinsung Integrated Co.,ltd.</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Jinsung Integrated Co.,ltd.</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>104934</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Mapo-gu</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Seoul</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>96-24, Sinjeong-dong</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>121-140</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>https://jsjuru.com</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr"/>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>bbcock@naver.com</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>+82 2-718-0744</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="inlineStr">
+        <is>
+          <t>1976</t>
+        </is>
+      </c>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>1058103811</t>
+        </is>
+      </c>
+      <c r="R154" s="2" t="inlineStr"/>
+      <c r="S154" s="2" t="inlineStr"/>
+      <c r="T154" s="2" t="inlineStr"/>
+      <c r="U154" s="2" t="inlineStr"/>
+      <c r="V154" s="2" t="inlineStr"/>
+      <c r="W154" s="2" t="inlineStr">
+        <is>
+          <t>Bae Sang-</t>
+        </is>
+      </c>
+      <c r="X154" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y154" s="2" t="inlineStr"/>
+      <c r="Z154" s="2" t="inlineStr"/>
+      <c r="AA154" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Korea.xlsx
+++ b/BWI/bestwine_output/bestwine_South Korea.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA154"/>
+  <dimension ref="A1:AA155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16726,6 +16726,87 @@
       <c r="Z154" s="2" t="inlineStr"/>
       <c r="AA154" s="2" t="inlineStr"/>
     </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Ssc Int.</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Ssc Int.</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>104779</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Changwon-si</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Gyeongsangnam-do</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Building 1st floor, 529, 3.15-daero, Masanwon-gu</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>630-010</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>http://wineart.or.kr</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr"/>
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr"/>
+      <c r="M155" s="2" t="inlineStr"/>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>sscwineart@naver.com</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>+82 1566-0890</t>
+        </is>
+      </c>
+      <c r="P155" s="2" t="inlineStr"/>
+      <c r="Q155" s="2" t="inlineStr"/>
+      <c r="R155" s="2" t="inlineStr"/>
+      <c r="S155" s="2" t="inlineStr"/>
+      <c r="T155" s="2" t="inlineStr"/>
+      <c r="U155" s="2" t="inlineStr"/>
+      <c r="V155" s="2" t="inlineStr"/>
+      <c r="W155" s="2" t="inlineStr">
+        <is>
+          <t>Sang-ho Hwang</t>
+        </is>
+      </c>
+      <c r="X155" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y155" s="2" t="inlineStr"/>
+      <c r="Z155" s="2" t="inlineStr"/>
+      <c r="AA155" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Korea.xlsx
+++ b/BWI/bestwine_output/bestwine_South Korea.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA155"/>
+  <dimension ref="A1:AA156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16807,6 +16807,87 @@
       <c r="Z155" s="2" t="inlineStr"/>
       <c r="AA155" s="2" t="inlineStr"/>
     </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Ssc Int.</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Ssc Int.</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>104779</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Changwon-si</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Gyeongsangnam-do</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Building 1st floor, 529, 3.15-daero, Masanwon-gu</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>630-010</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>http://wineart.or.kr</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr"/>
+      <c r="M156" s="2" t="inlineStr"/>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>sscwineart@naver.com</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>+82 1566-0890</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="inlineStr"/>
+      <c r="Q156" s="2" t="inlineStr"/>
+      <c r="R156" s="2" t="inlineStr"/>
+      <c r="S156" s="2" t="inlineStr"/>
+      <c r="T156" s="2" t="inlineStr"/>
+      <c r="U156" s="2" t="inlineStr"/>
+      <c r="V156" s="2" t="inlineStr"/>
+      <c r="W156" s="2" t="inlineStr">
+        <is>
+          <t>Sang-ho Hwang</t>
+        </is>
+      </c>
+      <c r="X156" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y156" s="2" t="inlineStr"/>
+      <c r="Z156" s="2" t="inlineStr"/>
+      <c r="AA156" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Korea.xlsx
+++ b/BWI/bestwine_output/bestwine_South Korea.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA156"/>
+  <dimension ref="A1:AA157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16888,6 +16888,87 @@
       <c r="Z156" s="2" t="inlineStr"/>
       <c r="AA156" s="2" t="inlineStr"/>
     </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Ssc Int.</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Ssc Int.</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>104779</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Changwon-si</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Gyeongsangnam-do</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Building 1st floor, 529, 3.15-daero, Masanwon-gu</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>630-010</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>http://wineart.or.kr</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr"/>
+      <c r="M157" s="2" t="inlineStr"/>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>sscwineart@naver.com</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>+82 1566-0890</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="inlineStr"/>
+      <c r="Q157" s="2" t="inlineStr"/>
+      <c r="R157" s="2" t="inlineStr"/>
+      <c r="S157" s="2" t="inlineStr"/>
+      <c r="T157" s="2" t="inlineStr"/>
+      <c r="U157" s="2" t="inlineStr"/>
+      <c r="V157" s="2" t="inlineStr"/>
+      <c r="W157" s="2" t="inlineStr">
+        <is>
+          <t>Sang-ho Hwang</t>
+        </is>
+      </c>
+      <c r="X157" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y157" s="2" t="inlineStr"/>
+      <c r="Z157" s="2" t="inlineStr"/>
+      <c r="AA157" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Korea.xlsx
+++ b/BWI/bestwine_output/bestwine_South Korea.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16969,6 +16969,87 @@
       <c r="Z157" s="2" t="inlineStr"/>
       <c r="AA157" s="2" t="inlineStr"/>
     </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Ssc Int.</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Ssc Int.</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>104779</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Changwon-si</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Gyeongsangnam-do</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Building 1st floor, 529, 3.15-daero, Masanwon-gu</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>630-010</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>http://wineart.or.kr</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr"/>
+      <c r="M158" s="2" t="inlineStr"/>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>sscwineart@naver.com</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>+82 1566-0890</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="inlineStr"/>
+      <c r="Q158" s="2" t="inlineStr"/>
+      <c r="R158" s="2" t="inlineStr"/>
+      <c r="S158" s="2" t="inlineStr"/>
+      <c r="T158" s="2" t="inlineStr"/>
+      <c r="U158" s="2" t="inlineStr"/>
+      <c r="V158" s="2" t="inlineStr"/>
+      <c r="W158" s="2" t="inlineStr">
+        <is>
+          <t>Sang-ho Hwang</t>
+        </is>
+      </c>
+      <c r="X158" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y158" s="2" t="inlineStr"/>
+      <c r="Z158" s="2" t="inlineStr"/>
+      <c r="AA158" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Korea.xlsx
+++ b/BWI/bestwine_output/bestwine_South Korea.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA158"/>
+  <dimension ref="A1:AA159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17050,6 +17050,87 @@
       <c r="Z158" s="2" t="inlineStr"/>
       <c r="AA158" s="2" t="inlineStr"/>
     </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Ssc Int.</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Ssc Int.</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>104779</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Changwon-si</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Gyeongsangnam-do</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Building 1st floor, 529, 3.15-daero, Masanwon-gu</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>630-010</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>http://wineart.or.kr</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr"/>
+      <c r="M159" s="2" t="inlineStr"/>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>sscwineart@naver.com</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>+82 1566-0890</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="inlineStr"/>
+      <c r="Q159" s="2" t="inlineStr"/>
+      <c r="R159" s="2" t="inlineStr"/>
+      <c r="S159" s="2" t="inlineStr"/>
+      <c r="T159" s="2" t="inlineStr"/>
+      <c r="U159" s="2" t="inlineStr"/>
+      <c r="V159" s="2" t="inlineStr"/>
+      <c r="W159" s="2" t="inlineStr">
+        <is>
+          <t>Sang-ho Hwang</t>
+        </is>
+      </c>
+      <c r="X159" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y159" s="2" t="inlineStr"/>
+      <c r="Z159" s="2" t="inlineStr"/>
+      <c r="AA159" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
